--- a/public/tally_templates/STMJ.xlsx
+++ b/public/tally_templates/STMJ.xlsx
@@ -7262,7 +7262,6 @@
       </c>
       <c r="H61" s="404">
         <f>H12</f>
-        <v>NaN</v>
       </c>
       <c r="I61" s="405" t="s">
         <v>76</v>

--- a/public/tally_templates/STMJ.xlsx
+++ b/public/tally_templates/STMJ.xlsx
@@ -1413,7 +1413,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac x16r2">
   <numFmts count="8">
     <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * -#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* (#,##0);_(* &quot;-&quot;_);_(@_)"/>
@@ -3090,7 +3090,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="476">
+  <cellXfs count="503">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -4485,6 +4485,87 @@
     <xf numFmtId="171" fontId="42" fillId="0" borderId="103" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="101" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="103" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="103" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="103" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="103" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4492,11 +4573,11 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <ns3:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <ns4:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -4930,7 +5011,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y186"/>
   <sheetFormatPr defaultRowHeight="19.2" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
@@ -5692,14 +5773,14 @@
       <c r="D7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="168" t="s">
         <v>60</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="200">
+      <c r="H7" s="489">
         <v>46224</v>
       </c>
       <c r="I7" s="8"/>
@@ -5729,14 +5810,14 @@
       <c r="D8" s="393" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="168">
         <v>7</v>
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="168" t="s">
         <v>152</v>
       </c>
       <c r="I8" s="8"/>
@@ -7120,7 +7201,7 @@
       <c r="G57" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="H57" s="8" t="s">
+      <c r="H57" s="168" t="s">
         <v>152</v>
       </c>
       <c r="I57" s="8"/>
@@ -7245,27 +7326,17 @@
       <c r="Y60" s="95"/>
     </row>
     <row r="61" ht="16.95" customHeight="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="400" t="s">
-        <v>163</v>
-      </c>
+      <c r="A61" s="400"/>
       <c r="B61" s="401"/>
-      <c r="C61" s="402" t="s">
-        <v>164</v>
-      </c>
+      <c r="C61" s="402"/>
       <c r="D61" s="401"/>
       <c r="E61" s="401"/>
-      <c r="F61" s="403">
-        <v>-25</v>
-      </c>
-      <c r="G61" s="403">
-        <v>-25</v>
-      </c>
+      <c r="F61" s="403"/>
+      <c r="G61" s="403"/>
       <c r="H61" s="404">
         <f>H12</f>
       </c>
-      <c r="I61" s="405" t="s">
-        <v>76</v>
-      </c>
+      <c r="I61" s="405"/>
       <c r="J61" s="42"/>
       <c r="K61" s="42"/>
       <c r="L61" s="42"/>
@@ -7284,27 +7355,15 @@
       <c r="Y61" s="42"/>
     </row>
     <row r="62" ht="16.95" customHeight="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="406" t="s">
-        <v>165</v>
-      </c>
+      <c r="A62" s="406"/>
       <c r="B62" s="407"/>
-      <c r="C62" s="408" t="s">
-        <v>164</v>
-      </c>
+      <c r="C62" s="408"/>
       <c r="D62" s="407"/>
       <c r="E62" s="407"/>
-      <c r="F62" s="409">
-        <v>-18</v>
-      </c>
-      <c r="G62" s="409">
-        <v>-18.1</v>
-      </c>
-      <c r="H62" s="410" t="s">
-        <v>166</v>
-      </c>
-      <c r="I62" s="411" t="s">
-        <v>72</v>
-      </c>
+      <c r="F62" s="409"/>
+      <c r="G62" s="409"/>
+      <c r="H62" s="410"/>
+      <c r="I62" s="411"/>
       <c r="J62" s="42"/>
       <c r="K62" s="42"/>
       <c r="L62" s="42"/>
@@ -7323,27 +7382,15 @@
       <c r="Y62" s="42"/>
     </row>
     <row r="63" ht="16.95" customHeight="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="406" t="s">
-        <v>167</v>
-      </c>
+      <c r="A63" s="406"/>
       <c r="B63" s="407"/>
-      <c r="C63" s="408" t="s">
-        <v>164</v>
-      </c>
+      <c r="C63" s="408"/>
       <c r="D63" s="407"/>
       <c r="E63" s="407"/>
-      <c r="F63" s="412">
-        <v>-2.5</v>
-      </c>
-      <c r="G63" s="412">
-        <v>-2.5</v>
-      </c>
-      <c r="H63" s="410" t="s">
-        <v>166</v>
-      </c>
-      <c r="I63" s="411" t="s">
-        <v>72</v>
-      </c>
+      <c r="F63" s="412"/>
+      <c r="G63" s="412"/>
+      <c r="H63" s="410"/>
+      <c r="I63" s="411"/>
       <c r="J63" s="42"/>
       <c r="K63" s="42"/>
       <c r="L63" s="42"/>
@@ -7362,27 +7409,15 @@
       <c r="Y63" s="42"/>
     </row>
     <row r="64" ht="16.95" customHeight="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="411" t="s">
-        <v>168</v>
-      </c>
+      <c r="A64" s="411"/>
       <c r="B64" s="407"/>
-      <c r="C64" s="408" t="s">
-        <v>164</v>
-      </c>
+      <c r="C64" s="408"/>
       <c r="D64" s="407"/>
       <c r="E64" s="407"/>
-      <c r="F64" s="409">
-        <v>-18</v>
-      </c>
-      <c r="G64" s="409">
-        <v>-18.1</v>
-      </c>
-      <c r="H64" s="410" t="s">
-        <v>166</v>
-      </c>
-      <c r="I64" s="411" t="s">
-        <v>72</v>
-      </c>
+      <c r="F64" s="409"/>
+      <c r="G64" s="409"/>
+      <c r="H64" s="410"/>
+      <c r="I64" s="411"/>
       <c r="J64" s="413"/>
       <c r="K64" s="42"/>
       <c r="L64" s="42"/>
@@ -7401,27 +7436,15 @@
       <c r="Y64" s="42"/>
     </row>
     <row r="65" ht="16.95" customHeight="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="414" t="s">
-        <v>169</v>
-      </c>
+      <c r="A65" s="414"/>
       <c r="B65" s="415"/>
-      <c r="C65" s="416" t="s">
-        <v>164</v>
-      </c>
+      <c r="C65" s="416"/>
       <c r="D65" s="415"/>
       <c r="E65" s="415"/>
-      <c r="F65" s="417">
-        <v>-18</v>
-      </c>
-      <c r="G65" s="417">
-        <v>-18</v>
-      </c>
-      <c r="H65" s="418" t="s">
-        <v>166</v>
-      </c>
-      <c r="I65" s="414" t="s">
-        <v>72</v>
-      </c>
+      <c r="F65" s="417"/>
+      <c r="G65" s="417"/>
+      <c r="H65" s="418"/>
+      <c r="I65" s="414"/>
       <c r="J65" s="413"/>
       <c r="K65" s="42"/>
       <c r="L65" s="42"/>
@@ -7440,27 +7463,15 @@
       <c r="Y65" s="42"/>
     </row>
     <row r="66" ht="16.95" customHeight="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="405" t="s">
-        <v>170</v>
-      </c>
+      <c r="A66" s="405"/>
       <c r="B66" s="401"/>
-      <c r="C66" s="402" t="s">
-        <v>164</v>
-      </c>
+      <c r="C66" s="402"/>
       <c r="D66" s="401"/>
       <c r="E66" s="401"/>
-      <c r="F66" s="403">
-        <v>-18</v>
-      </c>
-      <c r="G66" s="403">
-        <v>-18</v>
-      </c>
-      <c r="H66" s="404" t="s">
-        <v>166</v>
-      </c>
-      <c r="I66" s="405" t="s">
-        <v>72</v>
-      </c>
+      <c r="F66" s="403"/>
+      <c r="G66" s="403"/>
+      <c r="H66" s="404"/>
+      <c r="I66" s="405"/>
       <c r="J66" s="413"/>
       <c r="K66" s="42"/>
       <c r="L66" s="42"/>
@@ -7479,27 +7490,15 @@
       <c r="Y66" s="42"/>
     </row>
     <row r="67" ht="16.95" customHeight="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="406" t="s">
-        <v>171</v>
-      </c>
+      <c r="A67" s="406"/>
       <c r="B67" s="407"/>
-      <c r="C67" s="408" t="s">
-        <v>164</v>
-      </c>
+      <c r="C67" s="408"/>
       <c r="D67" s="407"/>
       <c r="E67" s="407"/>
-      <c r="F67" s="409">
-        <v>-18</v>
-      </c>
-      <c r="G67" s="409">
-        <v>-17.9</v>
-      </c>
-      <c r="H67" s="410" t="s">
-        <v>166</v>
-      </c>
-      <c r="I67" s="411" t="s">
-        <v>76</v>
-      </c>
+      <c r="F67" s="409"/>
+      <c r="G67" s="409"/>
+      <c r="H67" s="410"/>
+      <c r="I67" s="411"/>
       <c r="J67" s="413"/>
       <c r="K67" s="42"/>
       <c r="L67" s="42"/>
@@ -7518,27 +7517,15 @@
       <c r="Y67" s="42"/>
     </row>
     <row r="68" ht="16.95" customHeight="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="406" t="s">
-        <v>172</v>
-      </c>
+      <c r="A68" s="406"/>
       <c r="B68" s="407"/>
-      <c r="C68" s="408" t="s">
-        <v>164</v>
-      </c>
+      <c r="C68" s="408"/>
       <c r="D68" s="407"/>
       <c r="E68" s="407"/>
-      <c r="F68" s="409">
-        <v>-2.5</v>
-      </c>
-      <c r="G68" s="409">
-        <v>-2.5</v>
-      </c>
-      <c r="H68" s="410" t="s">
-        <v>166</v>
-      </c>
-      <c r="I68" s="411" t="s">
-        <v>76</v>
-      </c>
+      <c r="F68" s="409"/>
+      <c r="G68" s="409"/>
+      <c r="H68" s="410"/>
+      <c r="I68" s="411"/>
       <c r="J68" s="413"/>
       <c r="K68" s="42"/>
       <c r="L68" s="42"/>
@@ -7557,27 +7544,15 @@
       <c r="Y68" s="42"/>
     </row>
     <row r="69" ht="16.95" customHeight="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="411" t="s">
-        <v>173</v>
-      </c>
+      <c r="A69" s="411"/>
       <c r="B69" s="407"/>
-      <c r="C69" s="408" t="s">
-        <v>164</v>
-      </c>
+      <c r="C69" s="408"/>
       <c r="D69" s="407"/>
       <c r="E69" s="407"/>
-      <c r="F69" s="409">
-        <v>-2.5</v>
-      </c>
-      <c r="G69" s="409">
-        <v>-2.5</v>
-      </c>
-      <c r="H69" s="410" t="s">
-        <v>166</v>
-      </c>
-      <c r="I69" s="411" t="s">
-        <v>76</v>
-      </c>
+      <c r="F69" s="409"/>
+      <c r="G69" s="409"/>
+      <c r="H69" s="410"/>
+      <c r="I69" s="411"/>
       <c r="J69" s="42"/>
       <c r="K69" s="42"/>
       <c r="L69" s="42"/>
@@ -7596,27 +7571,15 @@
       <c r="Y69" s="42"/>
     </row>
     <row r="70" ht="16.95" customHeight="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="419" t="s">
-        <v>174</v>
-      </c>
+      <c r="A70" s="419"/>
       <c r="B70" s="415"/>
-      <c r="C70" s="416" t="s">
-        <v>164</v>
-      </c>
+      <c r="C70" s="416"/>
       <c r="D70" s="415"/>
       <c r="E70" s="415"/>
-      <c r="F70" s="417">
-        <v>-25</v>
-      </c>
-      <c r="G70" s="417">
-        <v>-25.1</v>
-      </c>
-      <c r="H70" s="418" t="s">
-        <v>166</v>
-      </c>
-      <c r="I70" s="414" t="s">
-        <v>76</v>
-      </c>
+      <c r="F70" s="417"/>
+      <c r="G70" s="417"/>
+      <c r="H70" s="418"/>
+      <c r="I70" s="414"/>
       <c r="J70" s="42"/>
       <c r="K70" s="42"/>
       <c r="L70" s="42"/>
@@ -7635,27 +7598,15 @@
       <c r="Y70" s="42"/>
     </row>
     <row r="71" ht="16.95" customHeight="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="422" t="s">
-        <v>175</v>
-      </c>
+      <c r="A71" s="422"/>
       <c r="B71" s="401"/>
-      <c r="C71" s="402" t="s">
-        <v>164</v>
-      </c>
+      <c r="C71" s="402"/>
       <c r="D71" s="401"/>
       <c r="E71" s="401"/>
-      <c r="F71" s="421">
-        <v>-25</v>
-      </c>
-      <c r="G71" s="421">
-        <v>-25</v>
-      </c>
-      <c r="H71" s="404" t="s">
-        <v>166</v>
-      </c>
-      <c r="I71" s="423" t="s">
-        <v>76</v>
-      </c>
+      <c r="F71" s="421"/>
+      <c r="G71" s="421"/>
+      <c r="H71" s="404"/>
+      <c r="I71" s="423"/>
       <c r="J71" s="42"/>
       <c r="K71" s="42"/>
       <c r="L71" s="42"/>
@@ -7674,27 +7625,15 @@
       <c r="Y71" s="42"/>
     </row>
     <row r="72" ht="16.95" customHeight="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="424" t="s">
-        <v>176</v>
-      </c>
+      <c r="A72" s="424"/>
       <c r="B72" s="407"/>
-      <c r="C72" s="408" t="s">
-        <v>164</v>
-      </c>
+      <c r="C72" s="408"/>
       <c r="D72" s="407"/>
       <c r="E72" s="407"/>
-      <c r="F72" s="412">
-        <v>-18</v>
-      </c>
-      <c r="G72" s="412">
-        <v>-18.1</v>
-      </c>
-      <c r="H72" s="410" t="s">
-        <v>166</v>
-      </c>
-      <c r="I72" s="425" t="s">
-        <v>76</v>
-      </c>
+      <c r="F72" s="412"/>
+      <c r="G72" s="412"/>
+      <c r="H72" s="410"/>
+      <c r="I72" s="425"/>
       <c r="J72" s="42"/>
       <c r="K72" s="42"/>
       <c r="L72" s="42"/>
@@ -7713,27 +7652,15 @@
       <c r="Y72" s="42"/>
     </row>
     <row r="73" ht="16.95" customHeight="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="424" t="s">
-        <v>177</v>
-      </c>
+      <c r="A73" s="424"/>
       <c r="B73" s="407"/>
-      <c r="C73" s="408" t="s">
-        <v>164</v>
-      </c>
+      <c r="C73" s="408"/>
       <c r="D73" s="407"/>
       <c r="E73" s="407"/>
-      <c r="F73" s="412">
-        <v>-25</v>
-      </c>
-      <c r="G73" s="412">
-        <v>-24.9</v>
-      </c>
-      <c r="H73" s="410" t="s">
-        <v>166</v>
-      </c>
-      <c r="I73" s="425" t="s">
-        <v>76</v>
-      </c>
+      <c r="F73" s="412"/>
+      <c r="G73" s="412"/>
+      <c r="H73" s="410"/>
+      <c r="I73" s="425"/>
       <c r="J73" s="42"/>
       <c r="K73" s="42"/>
       <c r="L73" s="42"/>
@@ -7752,27 +7679,15 @@
       <c r="Y73" s="42"/>
     </row>
     <row r="74" ht="16.95" customHeight="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="424" t="s">
-        <v>178</v>
-      </c>
+      <c r="A74" s="424"/>
       <c r="B74" s="407"/>
-      <c r="C74" s="408" t="s">
-        <v>164</v>
-      </c>
+      <c r="C74" s="408"/>
       <c r="D74" s="407"/>
       <c r="E74" s="407"/>
-      <c r="F74" s="412">
-        <v>-18</v>
-      </c>
-      <c r="G74" s="412">
-        <v>-17.9</v>
-      </c>
-      <c r="H74" s="410" t="s">
-        <v>166</v>
-      </c>
-      <c r="I74" s="425" t="s">
-        <v>76</v>
-      </c>
+      <c r="F74" s="412"/>
+      <c r="G74" s="412"/>
+      <c r="H74" s="410"/>
+      <c r="I74" s="425"/>
       <c r="J74" s="42"/>
       <c r="K74" s="42"/>
       <c r="L74" s="42"/>
@@ -7791,27 +7706,15 @@
       <c r="Y74" s="42"/>
     </row>
     <row r="75" ht="16.95" customHeight="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="426" t="s">
-        <v>179</v>
-      </c>
+      <c r="A75" s="426"/>
       <c r="B75" s="427"/>
-      <c r="C75" s="428" t="s">
-        <v>164</v>
-      </c>
+      <c r="C75" s="428"/>
       <c r="D75" s="427"/>
       <c r="E75" s="427"/>
-      <c r="F75" s="429">
-        <v>-2.5</v>
-      </c>
-      <c r="G75" s="429">
-        <v>-2.4</v>
-      </c>
-      <c r="H75" s="430" t="s">
-        <v>166</v>
-      </c>
-      <c r="I75" s="431" t="s">
-        <v>76</v>
-      </c>
+      <c r="F75" s="429"/>
+      <c r="G75" s="429"/>
+      <c r="H75" s="430"/>
+      <c r="I75" s="431"/>
       <c r="J75" s="42"/>
       <c r="K75" s="42"/>
       <c r="L75" s="42"/>
@@ -7830,27 +7733,15 @@
       <c r="Y75" s="42"/>
     </row>
     <row r="76" ht="16.95" customHeight="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="400" t="s">
-        <v>180</v>
-      </c>
+      <c r="A76" s="400"/>
       <c r="B76" s="401"/>
-      <c r="C76" s="402" t="s">
-        <v>164</v>
-      </c>
+      <c r="C76" s="402"/>
       <c r="D76" s="401"/>
       <c r="E76" s="401"/>
-      <c r="F76" s="403">
-        <v>-25</v>
-      </c>
-      <c r="G76" s="403">
-        <v>-25</v>
-      </c>
-      <c r="H76" s="404" t="s">
-        <v>166</v>
-      </c>
-      <c r="I76" s="405" t="s">
-        <v>76</v>
-      </c>
+      <c r="F76" s="403"/>
+      <c r="G76" s="403"/>
+      <c r="H76" s="404"/>
+      <c r="I76" s="405"/>
       <c r="J76" s="42"/>
       <c r="K76" s="42"/>
       <c r="L76" s="42"/>
@@ -7869,27 +7760,15 @@
       <c r="Y76" s="42"/>
     </row>
     <row r="77" ht="16.95" customHeight="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="424" t="s">
-        <v>181</v>
-      </c>
+      <c r="A77" s="424"/>
       <c r="B77" s="407"/>
-      <c r="C77" s="408" t="s">
-        <v>164</v>
-      </c>
+      <c r="C77" s="408"/>
       <c r="D77" s="407"/>
       <c r="E77" s="407"/>
-      <c r="F77" s="412">
-        <v>0</v>
-      </c>
-      <c r="G77" s="412">
-        <v>0.1</v>
-      </c>
-      <c r="H77" s="410" t="s">
-        <v>166</v>
-      </c>
-      <c r="I77" s="425" t="s">
-        <v>76</v>
-      </c>
+      <c r="F77" s="412"/>
+      <c r="G77" s="412"/>
+      <c r="H77" s="410"/>
+      <c r="I77" s="425"/>
       <c r="J77" s="42"/>
       <c r="K77" s="42"/>
       <c r="L77" s="42"/>
@@ -7908,27 +7787,15 @@
       <c r="Y77" s="42"/>
     </row>
     <row r="78" ht="16.95" customHeight="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="424" t="s">
-        <v>182</v>
-      </c>
+      <c r="A78" s="424"/>
       <c r="B78" s="407"/>
-      <c r="C78" s="408" t="s">
-        <v>164</v>
-      </c>
+      <c r="C78" s="408"/>
       <c r="D78" s="407"/>
       <c r="E78" s="407"/>
-      <c r="F78" s="412">
-        <v>-25</v>
-      </c>
-      <c r="G78" s="412">
-        <v>-25</v>
-      </c>
-      <c r="H78" s="410" t="s">
-        <v>166</v>
-      </c>
-      <c r="I78" s="425" t="s">
-        <v>76</v>
-      </c>
+      <c r="F78" s="412"/>
+      <c r="G78" s="412"/>
+      <c r="H78" s="410"/>
+      <c r="I78" s="425"/>
       <c r="J78" s="42"/>
       <c r="K78" s="42"/>
       <c r="L78" s="42"/>
@@ -7947,27 +7814,15 @@
       <c r="Y78" s="42"/>
     </row>
     <row r="79" ht="16.95" customHeight="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="424" t="s">
-        <v>183</v>
-      </c>
+      <c r="A79" s="424"/>
       <c r="B79" s="407"/>
-      <c r="C79" s="408" t="s">
-        <v>164</v>
-      </c>
+      <c r="C79" s="408"/>
       <c r="D79" s="407"/>
       <c r="E79" s="407"/>
-      <c r="F79" s="412">
-        <v>-18</v>
-      </c>
-      <c r="G79" s="412">
-        <v>-18</v>
-      </c>
-      <c r="H79" s="410" t="s">
-        <v>166</v>
-      </c>
-      <c r="I79" s="425" t="s">
-        <v>76</v>
-      </c>
+      <c r="F79" s="412"/>
+      <c r="G79" s="412"/>
+      <c r="H79" s="410"/>
+      <c r="I79" s="425"/>
       <c r="J79" s="42"/>
       <c r="K79" s="42"/>
       <c r="L79" s="42"/>
@@ -7986,27 +7841,15 @@
       <c r="Y79" s="42"/>
     </row>
     <row r="80" ht="16.95" customHeight="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="432" t="s">
-        <v>184</v>
-      </c>
+      <c r="A80" s="432"/>
       <c r="B80" s="415"/>
-      <c r="C80" s="416" t="s">
-        <v>164</v>
-      </c>
+      <c r="C80" s="416"/>
       <c r="D80" s="415"/>
       <c r="E80" s="415"/>
-      <c r="F80" s="420">
-        <v>-25</v>
-      </c>
-      <c r="G80" s="420">
-        <v>-25</v>
-      </c>
-      <c r="H80" s="418" t="s">
-        <v>166</v>
-      </c>
-      <c r="I80" s="433" t="s">
-        <v>76</v>
-      </c>
+      <c r="F80" s="420"/>
+      <c r="G80" s="420"/>
+      <c r="H80" s="418"/>
+      <c r="I80" s="433"/>
       <c r="J80" s="42"/>
       <c r="K80" s="42"/>
       <c r="L80" s="42"/>
@@ -8025,27 +7868,15 @@
       <c r="Y80" s="42"/>
     </row>
     <row r="81" ht="16.95" customHeight="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="422" t="s">
-        <v>185</v>
-      </c>
+      <c r="A81" s="422"/>
       <c r="B81" s="401"/>
-      <c r="C81" s="402" t="s">
-        <v>164</v>
-      </c>
+      <c r="C81" s="402"/>
       <c r="D81" s="401"/>
       <c r="E81" s="401"/>
-      <c r="F81" s="421">
-        <v>-18</v>
-      </c>
-      <c r="G81" s="421">
-        <v>-18.1</v>
-      </c>
-      <c r="H81" s="404" t="s">
-        <v>166</v>
-      </c>
-      <c r="I81" s="423" t="s">
-        <v>72</v>
-      </c>
+      <c r="F81" s="421"/>
+      <c r="G81" s="421"/>
+      <c r="H81" s="404"/>
+      <c r="I81" s="423"/>
       <c r="J81" s="42"/>
       <c r="K81" s="42"/>
       <c r="L81" s="42"/>
@@ -8064,27 +7895,15 @@
       <c r="Y81" s="42"/>
     </row>
     <row r="82" ht="16.95" customHeight="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="424" t="s">
-        <v>186</v>
-      </c>
+      <c r="A82" s="424"/>
       <c r="B82" s="407"/>
-      <c r="C82" s="408" t="s">
-        <v>164</v>
-      </c>
+      <c r="C82" s="408"/>
       <c r="D82" s="407"/>
       <c r="E82" s="407"/>
-      <c r="F82" s="412">
-        <v>-18</v>
-      </c>
-      <c r="G82" s="412">
-        <v>-17.9</v>
-      </c>
-      <c r="H82" s="410" t="s">
-        <v>166</v>
-      </c>
-      <c r="I82" s="425" t="s">
-        <v>72</v>
-      </c>
+      <c r="F82" s="412"/>
+      <c r="G82" s="412"/>
+      <c r="H82" s="410"/>
+      <c r="I82" s="425"/>
       <c r="J82" s="42"/>
       <c r="K82" s="42"/>
       <c r="L82" s="42"/>
@@ -8103,27 +7922,15 @@
       <c r="Y82" s="42"/>
     </row>
     <row r="83" ht="16.95" customHeight="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="424" t="s">
-        <v>187</v>
-      </c>
+      <c r="A83" s="424"/>
       <c r="B83" s="407"/>
-      <c r="C83" s="408" t="s">
-        <v>164</v>
-      </c>
+      <c r="C83" s="408"/>
       <c r="D83" s="407"/>
       <c r="E83" s="407"/>
-      <c r="F83" s="409">
-        <v>-18</v>
-      </c>
-      <c r="G83" s="409">
-        <v>-18.1</v>
-      </c>
-      <c r="H83" s="410" t="s">
-        <v>166</v>
-      </c>
-      <c r="I83" s="425" t="s">
-        <v>76</v>
-      </c>
+      <c r="F83" s="409"/>
+      <c r="G83" s="409"/>
+      <c r="H83" s="410"/>
+      <c r="I83" s="425"/>
       <c r="J83" s="42"/>
       <c r="K83" s="42"/>
       <c r="L83" s="42"/>
@@ -8142,27 +7949,15 @@
       <c r="Y83" s="42"/>
     </row>
     <row r="84" ht="16.95" customHeight="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="424" t="s">
-        <v>188</v>
-      </c>
+      <c r="A84" s="424"/>
       <c r="B84" s="407"/>
-      <c r="C84" s="408" t="s">
-        <v>164</v>
-      </c>
+      <c r="C84" s="408"/>
       <c r="D84" s="407"/>
       <c r="E84" s="407"/>
-      <c r="F84" s="409">
-        <v>-18</v>
-      </c>
-      <c r="G84" s="409">
-        <v>-18</v>
-      </c>
-      <c r="H84" s="410" t="s">
-        <v>166</v>
-      </c>
-      <c r="I84" s="425" t="s">
-        <v>72</v>
-      </c>
+      <c r="F84" s="409"/>
+      <c r="G84" s="409"/>
+      <c r="H84" s="410"/>
+      <c r="I84" s="425"/>
       <c r="J84" s="42"/>
       <c r="K84" s="42"/>
       <c r="L84" s="42"/>
@@ -8181,27 +7976,15 @@
       <c r="Y84" s="42"/>
     </row>
     <row r="85" ht="16.95" customHeight="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="424" t="s">
-        <v>189</v>
-      </c>
+      <c r="A85" s="424"/>
       <c r="B85" s="407"/>
-      <c r="C85" s="408" t="s">
-        <v>164</v>
-      </c>
+      <c r="C85" s="408"/>
       <c r="D85" s="407"/>
       <c r="E85" s="407"/>
-      <c r="F85" s="409">
-        <v>-18</v>
-      </c>
-      <c r="G85" s="409">
-        <v>-18.1</v>
-      </c>
-      <c r="H85" s="410" t="s">
-        <v>166</v>
-      </c>
-      <c r="I85" s="425" t="s">
-        <v>72</v>
-      </c>
+      <c r="F85" s="409"/>
+      <c r="G85" s="409"/>
+      <c r="H85" s="410"/>
+      <c r="I85" s="425"/>
       <c r="J85" s="42"/>
       <c r="K85" s="42"/>
       <c r="L85" s="42"/>
@@ -8769,14 +8552,14 @@
       <c r="D105" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E105" s="8" t="s">
+      <c r="E105" s="168" t="s">
         <v>84</v>
       </c>
       <c r="F105" s="8"/>
       <c r="G105" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="H105" s="200">
+      <c r="H105" s="489">
         <v>46225</v>
       </c>
       <c r="I105" s="8"/>
@@ -8806,14 +8589,14 @@
       <c r="D106" s="393" t="s">
         <v>7</v>
       </c>
-      <c r="E106" s="8">
+      <c r="E106" s="168">
         <v>7</v>
       </c>
       <c r="F106" s="8"/>
       <c r="G106" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="H106" s="8" t="s">
+      <c r="H106" s="168" t="s">
         <v>152</v>
       </c>
       <c r="I106" s="8"/>
@@ -8938,27 +8721,17 @@
       <c r="Y109" s="95"/>
     </row>
     <row r="110" ht="19.95" customHeight="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="400" t="s">
-        <v>197</v>
-      </c>
+      <c r="A110" s="400"/>
       <c r="B110" s="401"/>
-      <c r="C110" s="402" t="s">
-        <v>198</v>
-      </c>
+      <c r="C110" s="402"/>
       <c r="D110" s="401"/>
       <c r="E110" s="401"/>
-      <c r="F110" s="403">
-        <v>25</v>
-      </c>
-      <c r="G110" s="403">
-        <v>25.5</v>
-      </c>
+      <c r="F110" s="403"/>
+      <c r="G110" s="403"/>
       <c r="H110" s="404" t="s">
         <v>199</v>
       </c>
-      <c r="I110" s="422" t="s">
-        <v>200</v>
-      </c>
+      <c r="I110" s="422"/>
       <c r="J110" s="42"/>
       <c r="K110" s="42"/>
       <c r="L110" s="42"/>
@@ -9966,7 +9739,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -10695,7 +10468,7 @@
       <c r="A6" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="488" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="3"/>
@@ -10707,7 +10480,7 @@
         <v>38</v>
       </c>
       <c r="I6" s="8"/>
-      <c r="J6" s="8" t="s">
+      <c r="J6" s="168" t="s">
         <v>84</v>
       </c>
       <c r="K6" s="8"/>
@@ -10717,7 +10490,7 @@
       <c r="O6" s="201" t="s">
         <v>61</v>
       </c>
-      <c r="P6" s="200">
+      <c r="P6" s="489">
         <v>46225</v>
       </c>
       <c r="Q6" s="8"/>
@@ -10761,7 +10534,7 @@
       <c r="A8" s="201" t="s">
         <v>62</v>
       </c>
-      <c r="B8" s="201" t="s">
+      <c r="B8" s="168" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="201"/>
@@ -10773,7 +10546,7 @@
         <v>85</v>
       </c>
       <c r="I8" s="8"/>
-      <c r="J8" s="8" t="s">
+      <c r="J8" s="168" t="s">
         <v>64</v>
       </c>
       <c r="K8" s="8"/>
@@ -10783,7 +10556,7 @@
       <c r="O8" s="201" t="s">
         <v>86</v>
       </c>
-      <c r="P8" s="8">
+      <c r="P8" s="168">
         <v>7</v>
       </c>
       <c r="Q8" s="8"/>
@@ -10823,7 +10596,7 @@
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
     </row>
-    <row r="10" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="205" t="s">
         <v>11</v>
       </c>
@@ -10864,7 +10637,7 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
     </row>
-    <row r="11" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="209"/>
       <c r="B11" s="209"/>
       <c r="C11" s="258"/>
@@ -11645,7 +11418,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -11941,7 +11714,7 @@
       <c r="X1" s="3"/>
       <c r="Y1" s="3"/>
     </row>
-    <row r="2" ht="21.75" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" ht="24.3" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="5" t="s">
         <v>1</v>
@@ -12001,7 +11774,7 @@
       <c r="A4" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="476" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="1"/>
@@ -12010,14 +11783,14 @@
       <c r="F4" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="12"/>
+      <c r="G4" s="477"/>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
       <c r="J4" s="1"/>
       <c r="K4" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="L4" s="14"/>
+      <c r="L4" s="478"/>
       <c r="M4" s="15"/>
       <c r="N4" s="15"/>
       <c r="O4" s="15"/>
@@ -12063,21 +11836,21 @@
       <c r="A6" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="18"/>
+      <c r="B6" s="477"/>
       <c r="C6" s="1"/>
       <c r="D6" s="2"/>
       <c r="E6" s="19"/>
       <c r="F6" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="12"/>
+      <c r="G6" s="477"/>
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
       <c r="J6" s="1"/>
       <c r="K6" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="L6" s="20" t="s">
+      <c r="L6" s="479" t="s">
         <v>9</v>
       </c>
       <c r="M6" s="20"/>
@@ -14663,7 +14436,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -15456,7 +15229,7 @@
       <c r="A6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="488" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="3"/>
@@ -15466,13 +15239,13 @@
       <c r="G6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="H6" s="8"/>
+      <c r="H6" s="168"/>
       <c r="I6" s="8"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="200"/>
+      <c r="L6" s="489"/>
       <c r="M6" s="8"/>
       <c r="N6" s="1"/>
       <c r="O6" s="3"/>
@@ -15518,7 +15291,7 @@
       <c r="A8" s="201" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="488" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="3"/>
@@ -15528,13 +15301,13 @@
       <c r="G8" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H8" s="8"/>
+      <c r="H8" s="168"/>
       <c r="I8" s="8"/>
       <c r="J8" s="3"/>
       <c r="K8" s="201" t="s">
         <v>42</v>
       </c>
-      <c r="L8" s="8"/>
+      <c r="L8" s="168"/>
       <c r="M8" s="8"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
@@ -15576,7 +15349,7 @@
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
     </row>
-    <row r="10" ht="14.4" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="202" t="s">
         <v>43</v>
       </c>
@@ -15621,7 +15394,7 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
     </row>
-    <row r="11" ht="14.4" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="206"/>
       <c r="B11" s="207"/>
       <c r="C11" s="208"/>
@@ -15663,7 +15436,7 @@
       <c r="J12" s="216"/>
       <c r="K12" s="210"/>
       <c r="L12" s="210"/>
-      <c r="M12" s="217"/>
+      <c r="M12" s="490"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
@@ -15690,7 +15463,7 @@
       <c r="J13" s="222"/>
       <c r="K13" s="218"/>
       <c r="L13" s="218"/>
-      <c r="M13" s="224"/>
+      <c r="M13" s="491"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
@@ -15717,7 +15490,7 @@
       <c r="J14" s="222"/>
       <c r="K14" s="218"/>
       <c r="L14" s="218"/>
-      <c r="M14" s="224"/>
+      <c r="M14" s="491"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
@@ -16448,7 +16221,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -17177,7 +16950,7 @@
       <c r="A6" s="201" t="s">
         <v>59</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="488" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="3"/>
@@ -17189,7 +16962,7 @@
         <v>38</v>
       </c>
       <c r="I6" s="8"/>
-      <c r="J6" s="8" t="s">
+      <c r="J6" s="168" t="s">
         <v>60</v>
       </c>
       <c r="K6" s="8"/>
@@ -17199,7 +16972,7 @@
       <c r="O6" s="201" t="s">
         <v>61</v>
       </c>
-      <c r="P6" s="200">
+      <c r="P6" s="489">
         <v>46224</v>
       </c>
       <c r="Q6" s="8"/>
@@ -17243,7 +17016,7 @@
       <c r="A8" s="201" t="s">
         <v>62</v>
       </c>
-      <c r="B8" s="201" t="s">
+      <c r="B8" s="168" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="201"/>
@@ -17255,7 +17028,7 @@
         <v>63</v>
       </c>
       <c r="I8" s="8"/>
-      <c r="J8" s="8" t="s">
+      <c r="J8" s="168" t="s">
         <v>64</v>
       </c>
       <c r="K8" s="8"/>
@@ -17265,7 +17038,7 @@
       <c r="O8" s="201" t="s">
         <v>65</v>
       </c>
-      <c r="P8" s="8">
+      <c r="P8" s="168">
         <v>7</v>
       </c>
       <c r="Q8" s="8"/>
@@ -17305,7 +17078,7 @@
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
     </row>
-    <row r="10" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="202" t="s">
         <v>11</v>
       </c>
@@ -17346,7 +17119,7 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
     </row>
-    <row r="11" ht="12" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="206"/>
       <c r="B11" s="206"/>
       <c r="C11" s="258"/>
@@ -17376,32 +17149,18 @@
       <c r="Y11" s="3"/>
     </row>
     <row r="12" ht="22.2" customHeight="1" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="261" t="s">
-        <v>71</v>
-      </c>
-      <c r="B12" s="261" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" s="169" t="s">
-        <v>73</v>
-      </c>
+      <c r="A12" s="261"/>
+      <c r="B12" s="261"/>
+      <c r="C12" s="169"/>
       <c r="D12" s="262"/>
       <c r="E12" s="176"/>
-      <c r="F12" s="263" t="s">
-        <v>74</v>
-      </c>
+      <c r="F12" s="263"/>
       <c r="G12" s="264"/>
       <c r="H12" s="264"/>
       <c r="I12" s="265"/>
-      <c r="J12" s="266">
-        <v>1</v>
-      </c>
-      <c r="K12" s="266" t="s">
-        <v>54</v>
-      </c>
-      <c r="L12" s="267" t="s">
-        <v>75</v>
-      </c>
+      <c r="J12" s="266"/>
+      <c r="K12" s="266"/>
+      <c r="L12" s="267"/>
       <c r="M12" s="267"/>
       <c r="N12" s="267"/>
       <c r="O12" s="267"/>
@@ -17417,32 +17176,18 @@
       <c r="Y12" s="3"/>
     </row>
     <row r="13" ht="22.2" customHeight="1" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="261" t="s">
-        <v>71</v>
-      </c>
-      <c r="B13" s="261" t="s">
-        <v>76</v>
-      </c>
-      <c r="C13" s="169" t="s">
-        <v>77</v>
-      </c>
+      <c r="A13" s="261"/>
+      <c r="B13" s="261"/>
+      <c r="C13" s="169"/>
       <c r="D13" s="262"/>
       <c r="E13" s="176"/>
-      <c r="F13" s="191" t="s">
-        <v>74</v>
-      </c>
+      <c r="F13" s="191"/>
       <c r="G13" s="56"/>
       <c r="H13" s="56"/>
       <c r="I13" s="58"/>
-      <c r="J13" s="55">
-        <v>1</v>
-      </c>
-      <c r="K13" s="55" t="s">
-        <v>54</v>
-      </c>
-      <c r="L13" s="268" t="s">
-        <v>78</v>
-      </c>
+      <c r="J13" s="55"/>
+      <c r="K13" s="55"/>
+      <c r="L13" s="268"/>
       <c r="M13" s="268"/>
       <c r="N13" s="268"/>
       <c r="O13" s="268"/>
@@ -17458,32 +17203,18 @@
       <c r="Y13" s="3"/>
     </row>
     <row r="14" ht="22.2" customHeight="1" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="261" t="s">
-        <v>71</v>
-      </c>
-      <c r="B14" s="261" t="s">
-        <v>76</v>
-      </c>
-      <c r="C14" s="169" t="s">
-        <v>79</v>
-      </c>
+      <c r="A14" s="261"/>
+      <c r="B14" s="261"/>
+      <c r="C14" s="169"/>
       <c r="D14" s="262"/>
       <c r="E14" s="176"/>
-      <c r="F14" s="191" t="s">
-        <v>74</v>
-      </c>
+      <c r="F14" s="191"/>
       <c r="G14" s="56"/>
       <c r="H14" s="56"/>
       <c r="I14" s="58"/>
-      <c r="J14" s="55">
-        <v>1</v>
-      </c>
-      <c r="K14" s="55" t="s">
-        <v>54</v>
-      </c>
-      <c r="L14" s="268" t="s">
-        <v>80</v>
-      </c>
+      <c r="J14" s="55"/>
+      <c r="K14" s="55"/>
+      <c r="L14" s="268"/>
       <c r="M14" s="268"/>
       <c r="N14" s="268"/>
       <c r="O14" s="268"/>
@@ -18139,7 +17870,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y208"/>
   <sheetFormatPr defaultRowHeight="15.6" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
   <cols>
@@ -18300,7 +18031,7 @@
       <c r="A6" s="42" t="s">
         <v>89</v>
       </c>
-      <c r="B6" s="290" t="s">
+      <c r="B6" s="495" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="290"/>
@@ -18309,7 +18040,7 @@
         <v>90</v>
       </c>
       <c r="F6" s="299"/>
-      <c r="G6" s="95" t="s">
+      <c r="G6" s="496" t="s">
         <v>60</v>
       </c>
       <c r="H6" s="95"/>
@@ -18317,7 +18048,7 @@
       <c r="J6" s="299" t="s">
         <v>91</v>
       </c>
-      <c r="K6" s="300">
+      <c r="K6" s="497">
         <v>46224</v>
       </c>
       <c r="L6" s="95"/>
@@ -18367,23 +18098,19 @@
         <v>92</v>
       </c>
       <c r="B8" s="250"/>
-      <c r="C8" s="42" t="s">
-        <v>73</v>
-      </c>
+      <c r="C8" s="498"/>
       <c r="D8" s="42"/>
       <c r="E8" s="299" t="s">
         <v>93</v>
       </c>
       <c r="F8" s="299"/>
-      <c r="G8" s="95" t="s">
-        <v>94</v>
-      </c>
+      <c r="G8" s="496"/>
       <c r="H8" s="95"/>
       <c r="I8" s="42"/>
       <c r="J8" s="299" t="s">
         <v>95</v>
       </c>
-      <c r="K8" s="95">
+      <c r="K8" s="496">
         <v>20</v>
       </c>
       <c r="L8" s="95">
@@ -18410,9 +18137,7 @@
         <v>96</v>
       </c>
       <c r="B9" s="250"/>
-      <c r="C9" s="42" t="s">
-        <v>72</v>
-      </c>
+      <c r="C9" s="42"/>
       <c r="D9" s="42"/>
       <c r="E9" s="42"/>
       <c r="F9" s="42"/>
@@ -19065,7 +18790,7 @@
       </c>
       <c r="B33" s="309"/>
       <c r="C33" s="309"/>
-      <c r="D33" s="310"/>
+      <c r="D33" s="499"/>
       <c r="E33" s="310"/>
       <c r="F33" s="310"/>
       <c r="G33" s="310"/>
@@ -19119,9 +18844,7 @@
     </row>
     <row r="35" ht="21.9" customHeight="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="311"/>
-      <c r="B35" s="313" t="s">
-        <v>75</v>
-      </c>
+      <c r="B35" s="313"/>
       <c r="C35" s="313"/>
       <c r="D35" s="313"/>
       <c r="E35" s="313"/>
@@ -19810,7 +19533,7 @@
       <c r="A58" s="42" t="s">
         <v>89</v>
       </c>
-      <c r="B58" s="290" t="s">
+      <c r="B58" s="495" t="s">
         <v>3</v>
       </c>
       <c r="C58" s="290"/>
@@ -19879,23 +19602,19 @@
         <v>92</v>
       </c>
       <c r="B60" s="250"/>
-      <c r="C60" s="42" t="s">
-        <v>77</v>
-      </c>
+      <c r="C60" s="498"/>
       <c r="D60" s="42"/>
       <c r="E60" s="299" t="s">
         <v>93</v>
       </c>
       <c r="F60" s="299"/>
-      <c r="G60" s="95" t="s">
-        <v>94</v>
-      </c>
+      <c r="G60" s="496"/>
       <c r="H60" s="95"/>
       <c r="I60" s="42"/>
       <c r="J60" s="299" t="s">
         <v>95</v>
       </c>
-      <c r="K60" s="95">
+      <c r="K60" s="496">
         <v>20</v>
       </c>
       <c r="L60" s="95">
@@ -19922,9 +19641,7 @@
         <v>96</v>
       </c>
       <c r="B61" s="250"/>
-      <c r="C61" s="42" t="s">
-        <v>76</v>
-      </c>
+      <c r="C61" s="42"/>
       <c r="D61" s="42"/>
       <c r="E61" s="42"/>
       <c r="F61" s="42"/>
@@ -20577,7 +20294,7 @@
       </c>
       <c r="B85" s="309"/>
       <c r="C85" s="309"/>
-      <c r="D85" s="310"/>
+      <c r="D85" s="499"/>
       <c r="E85" s="310"/>
       <c r="F85" s="310"/>
       <c r="G85" s="310"/>
@@ -20631,9 +20348,7 @@
     </row>
     <row r="87" ht="21.9" customHeight="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="311"/>
-      <c r="B87" s="313" t="s">
-        <v>78</v>
-      </c>
+      <c r="B87" s="313"/>
       <c r="C87" s="313"/>
       <c r="D87" s="313"/>
       <c r="E87" s="313"/>
@@ -21322,7 +21037,7 @@
       <c r="A110" s="42" t="s">
         <v>89</v>
       </c>
-      <c r="B110" s="290" t="s">
+      <c r="B110" s="495" t="s">
         <v>3</v>
       </c>
       <c r="C110" s="290"/>
@@ -21391,23 +21106,19 @@
         <v>92</v>
       </c>
       <c r="B112" s="250"/>
-      <c r="C112" s="42" t="s">
-        <v>79</v>
-      </c>
+      <c r="C112" s="498"/>
       <c r="D112" s="42"/>
       <c r="E112" s="299" t="s">
         <v>93</v>
       </c>
       <c r="F112" s="299"/>
-      <c r="G112" s="95" t="s">
-        <v>94</v>
-      </c>
+      <c r="G112" s="496"/>
       <c r="H112" s="95"/>
       <c r="I112" s="42"/>
       <c r="J112" s="299" t="s">
         <v>95</v>
       </c>
-      <c r="K112" s="95">
+      <c r="K112" s="496">
         <v>20</v>
       </c>
       <c r="L112" s="95">
@@ -21434,9 +21145,7 @@
         <v>96</v>
       </c>
       <c r="B113" s="250"/>
-      <c r="C113" s="42" t="s">
-        <v>76</v>
-      </c>
+      <c r="C113" s="42"/>
       <c r="D113" s="42"/>
       <c r="E113" s="42"/>
       <c r="F113" s="42"/>
@@ -22089,7 +21798,7 @@
       </c>
       <c r="B137" s="309"/>
       <c r="C137" s="309"/>
-      <c r="D137" s="310"/>
+      <c r="D137" s="499"/>
       <c r="E137" s="310"/>
       <c r="F137" s="310"/>
       <c r="G137" s="310"/>
@@ -22143,9 +21852,7 @@
     </row>
     <row r="139" ht="21.9" customHeight="1" spans="1:25" s="42" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="311"/>
-      <c r="B139" s="313" t="s">
-        <v>80</v>
-      </c>
+      <c r="B139" s="313"/>
       <c r="C139" s="313"/>
       <c r="D139" s="313"/>
       <c r="E139" s="313"/>
@@ -22494,7 +22201,7 @@
       <c r="A162" s="42" t="s">
         <v>89</v>
       </c>
-      <c r="B162" s="290" t="s">
+      <c r="B162" s="495" t="s">
         <v>3</v>
       </c>
       <c r="C162" s="290"/>
@@ -22503,7 +22210,7 @@
         <v>90</v>
       </c>
       <c r="F162" s="299"/>
-      <c r="G162" s="95" t="s">
+      <c r="G162" s="496" t="s">
         <v>84</v>
       </c>
       <c r="H162" s="95"/>
@@ -22511,7 +22218,7 @@
       <c r="J162" s="299" t="s">
         <v>91</v>
       </c>
-      <c r="K162" s="300">
+      <c r="K162" s="497">
         <v>46225</v>
       </c>
       <c r="L162" s="95"/>
@@ -22541,12 +22248,12 @@
         <v>93</v>
       </c>
       <c r="F164" s="299"/>
-      <c r="G164" s="95"/>
+      <c r="G164" s="496"/>
       <c r="H164" s="95"/>
       <c r="J164" s="299" t="s">
         <v>95</v>
       </c>
-      <c r="K164" s="95">
+      <c r="K164" s="496">
         <v>20</v>
       </c>
       <c r="L164" s="95">
@@ -22691,7 +22398,7 @@
       </c>
       <c r="B189" s="309"/>
       <c r="C189" s="309"/>
-      <c r="D189" s="310"/>
+      <c r="D189" s="499"/>
       <c r="E189" s="310"/>
       <c r="F189" s="310"/>
       <c r="G189" s="310"/>
@@ -23141,7 +22848,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -23934,7 +23641,7 @@
       <c r="A6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="488" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="3"/>
@@ -23944,13 +23651,13 @@
       <c r="G6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="H6" s="8"/>
+      <c r="H6" s="168"/>
       <c r="I6" s="8"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="200"/>
+      <c r="L6" s="489"/>
       <c r="M6" s="8"/>
       <c r="N6" s="1"/>
       <c r="O6" s="3"/>
@@ -23996,7 +23703,7 @@
       <c r="A8" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="488" t="s">
         <v>25</v>
       </c>
       <c r="C8" s="270"/>
@@ -24006,13 +23713,13 @@
       <c r="G8" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H8" s="8"/>
+      <c r="H8" s="168"/>
       <c r="I8" s="8"/>
       <c r="J8" s="3"/>
       <c r="K8" s="201" t="s">
         <v>42</v>
       </c>
-      <c r="L8" s="8"/>
+      <c r="L8" s="168"/>
       <c r="M8" s="8"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
@@ -24054,7 +23761,7 @@
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
     </row>
-    <row r="10" ht="14.4" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="202" t="s">
         <v>43</v>
       </c>
@@ -24099,7 +23806,7 @@
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
     </row>
-    <row r="11" ht="14.4" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" ht="16.2" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="206"/>
       <c r="B11" s="207"/>
       <c r="C11" s="208"/>
@@ -24133,15 +23840,15 @@
       <c r="B12" s="210"/>
       <c r="C12" s="210"/>
       <c r="D12" s="211"/>
-      <c r="E12" s="271"/>
-      <c r="F12" s="272"/>
+      <c r="E12" s="492"/>
+      <c r="F12" s="493"/>
       <c r="G12" s="210"/>
       <c r="H12" s="216"/>
       <c r="I12" s="273"/>
       <c r="J12" s="216"/>
       <c r="K12" s="210"/>
       <c r="L12" s="210"/>
-      <c r="M12" s="274"/>
+      <c r="M12" s="115"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
@@ -24160,15 +23867,15 @@
       <c r="B13" s="241"/>
       <c r="C13" s="241"/>
       <c r="D13" s="219"/>
-      <c r="E13" s="271"/>
-      <c r="F13" s="275"/>
+      <c r="E13" s="492"/>
+      <c r="F13" s="494"/>
       <c r="G13" s="218"/>
       <c r="H13" s="276"/>
       <c r="I13" s="277"/>
       <c r="J13" s="222"/>
       <c r="K13" s="218"/>
       <c r="L13" s="218"/>
-      <c r="M13" s="278"/>
+      <c r="M13" s="52"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
@@ -24187,15 +23894,15 @@
       <c r="B14" s="241"/>
       <c r="C14" s="241"/>
       <c r="D14" s="219"/>
-      <c r="E14" s="271"/>
-      <c r="F14" s="275"/>
+      <c r="E14" s="492"/>
+      <c r="F14" s="494"/>
       <c r="G14" s="218"/>
       <c r="H14" s="276"/>
       <c r="I14" s="277"/>
       <c r="J14" s="279"/>
       <c r="K14" s="218"/>
       <c r="L14" s="218"/>
-      <c r="M14" s="278"/>
+      <c r="M14" s="52"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
@@ -24214,15 +23921,15 @@
       <c r="B15" s="241"/>
       <c r="C15" s="241"/>
       <c r="D15" s="219"/>
-      <c r="E15" s="271"/>
-      <c r="F15" s="275"/>
+      <c r="E15" s="492"/>
+      <c r="F15" s="494"/>
       <c r="G15" s="218"/>
       <c r="H15" s="276"/>
       <c r="I15" s="277"/>
       <c r="J15" s="222"/>
       <c r="K15" s="218"/>
       <c r="L15" s="218"/>
-      <c r="M15" s="278"/>
+      <c r="M15" s="52"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
@@ -24241,15 +23948,15 @@
       <c r="B16" s="241"/>
       <c r="C16" s="241"/>
       <c r="D16" s="219"/>
-      <c r="E16" s="271"/>
-      <c r="F16" s="275"/>
+      <c r="E16" s="492"/>
+      <c r="F16" s="494"/>
       <c r="G16" s="218"/>
       <c r="H16" s="276"/>
       <c r="I16" s="277"/>
       <c r="J16" s="222"/>
       <c r="K16" s="218"/>
       <c r="L16" s="218"/>
-      <c r="M16" s="278"/>
+      <c r="M16" s="52"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
@@ -24268,15 +23975,15 @@
       <c r="B17" s="241"/>
       <c r="C17" s="241"/>
       <c r="D17" s="219"/>
-      <c r="E17" s="271"/>
-      <c r="F17" s="275"/>
+      <c r="E17" s="492"/>
+      <c r="F17" s="494"/>
       <c r="G17" s="218"/>
       <c r="H17" s="276"/>
       <c r="I17" s="277"/>
       <c r="J17" s="222"/>
       <c r="K17" s="218"/>
       <c r="L17" s="218"/>
-      <c r="M17" s="278"/>
+      <c r="M17" s="52"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
@@ -24295,15 +24002,15 @@
       <c r="B18" s="241"/>
       <c r="C18" s="241"/>
       <c r="D18" s="219"/>
-      <c r="E18" s="271"/>
-      <c r="F18" s="275"/>
+      <c r="E18" s="492"/>
+      <c r="F18" s="494"/>
       <c r="G18" s="218"/>
       <c r="H18" s="276"/>
       <c r="I18" s="277"/>
       <c r="J18" s="222"/>
       <c r="K18" s="218"/>
       <c r="L18" s="218"/>
-      <c r="M18" s="278"/>
+      <c r="M18" s="52"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
@@ -24322,15 +24029,15 @@
       <c r="B19" s="241"/>
       <c r="C19" s="241"/>
       <c r="D19" s="219"/>
-      <c r="E19" s="271"/>
-      <c r="F19" s="275"/>
+      <c r="E19" s="492"/>
+      <c r="F19" s="494"/>
       <c r="G19" s="218"/>
       <c r="H19" s="276"/>
       <c r="I19" s="277"/>
       <c r="J19" s="222"/>
       <c r="K19" s="218"/>
       <c r="L19" s="218"/>
-      <c r="M19" s="278"/>
+      <c r="M19" s="52"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
@@ -24977,7 +24684,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y22"/>
   <sheetFormatPr defaultRowHeight="13.2" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="7.5" customHeight="1"/>
   <cols>
@@ -26654,9 +26361,9 @@
       <c r="I11" s="470"/>
       <c r="J11" s="470"/>
       <c r="K11" s="470"/>
-      <c r="L11" s="473"/>
-      <c r="M11" s="473"/>
-      <c r="N11" s="473"/>
+      <c r="L11" s="502"/>
+      <c r="M11" s="502"/>
+      <c r="N11" s="502"/>
       <c r="O11" s="437"/>
       <c r="P11" s="437"/>
       <c r="Q11" s="434"/>
@@ -26681,9 +26388,9 @@
       <c r="I12" s="470"/>
       <c r="J12" s="470"/>
       <c r="K12" s="470"/>
-      <c r="L12" s="473"/>
-      <c r="M12" s="473"/>
-      <c r="N12" s="473"/>
+      <c r="L12" s="502"/>
+      <c r="M12" s="502"/>
+      <c r="N12" s="502"/>
       <c r="O12" s="437"/>
       <c r="P12" s="437"/>
       <c r="Q12" s="434"/>
@@ -26708,9 +26415,9 @@
       <c r="I13" s="470"/>
       <c r="J13" s="470"/>
       <c r="K13" s="470"/>
-      <c r="L13" s="473"/>
-      <c r="M13" s="473"/>
-      <c r="N13" s="473"/>
+      <c r="L13" s="502"/>
+      <c r="M13" s="502"/>
+      <c r="N13" s="502"/>
       <c r="O13" s="437"/>
       <c r="P13" s="437"/>
       <c r="Q13" s="434"/>
@@ -26735,9 +26442,9 @@
       <c r="I14" s="470"/>
       <c r="J14" s="470"/>
       <c r="K14" s="470"/>
-      <c r="L14" s="473"/>
-      <c r="M14" s="473"/>
-      <c r="N14" s="473"/>
+      <c r="L14" s="502"/>
+      <c r="M14" s="502"/>
+      <c r="N14" s="502"/>
       <c r="O14" s="437"/>
       <c r="P14" s="437"/>
       <c r="Q14" s="434"/>
@@ -26762,9 +26469,9 @@
       <c r="I15" s="470"/>
       <c r="J15" s="470"/>
       <c r="K15" s="470"/>
-      <c r="L15" s="473"/>
-      <c r="M15" s="473"/>
-      <c r="N15" s="473"/>
+      <c r="L15" s="502"/>
+      <c r="M15" s="502"/>
+      <c r="N15" s="502"/>
       <c r="O15" s="437"/>
       <c r="P15" s="437"/>
       <c r="Q15" s="434"/>
@@ -26789,9 +26496,9 @@
       <c r="I16" s="470"/>
       <c r="J16" s="470"/>
       <c r="K16" s="470"/>
-      <c r="L16" s="473"/>
-      <c r="M16" s="473"/>
-      <c r="N16" s="473"/>
+      <c r="L16" s="502"/>
+      <c r="M16" s="502"/>
+      <c r="N16" s="502"/>
       <c r="O16" s="437"/>
       <c r="P16" s="437"/>
       <c r="Q16" s="434"/>
@@ -26816,9 +26523,9 @@
       <c r="I17" s="470"/>
       <c r="J17" s="470"/>
       <c r="K17" s="470"/>
-      <c r="L17" s="473"/>
-      <c r="M17" s="473"/>
-      <c r="N17" s="473"/>
+      <c r="L17" s="502"/>
+      <c r="M17" s="502"/>
+      <c r="N17" s="502"/>
       <c r="O17" s="437"/>
       <c r="P17" s="437"/>
       <c r="Q17" s="434"/>
@@ -26989,7 +26696,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -27656,11 +27363,11 @@
       <c r="A6" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="9"/>
+      <c r="B6" s="476"/>
       <c r="C6" s="157" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="15"/>
+      <c r="D6" s="480"/>
       <c r="E6" s="15"/>
       <c r="F6" s="9"/>
       <c r="G6" s="158" t="s">
@@ -27719,17 +27426,17 @@
       <c r="A8" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="160"/>
+      <c r="B8" s="480"/>
       <c r="C8" s="157" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="15"/>
+      <c r="D8" s="480"/>
       <c r="E8" s="15"/>
       <c r="F8" s="157"/>
       <c r="G8" s="161" t="s">
         <v>30</v>
       </c>
-      <c r="H8" s="20"/>
+      <c r="H8" s="479"/>
       <c r="I8" s="9"/>
       <c r="J8" s="9"/>
       <c r="K8" s="9"/>
@@ -27867,7 +27574,7 @@
         <v>34</v>
       </c>
       <c r="B13" s="166"/>
-      <c r="C13" s="167"/>
+      <c r="C13" s="481"/>
       <c r="D13" s="167"/>
       <c r="E13" s="167"/>
       <c r="F13" s="167"/>
@@ -27894,7 +27601,7 @@
     <row r="14" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="169"/>
       <c r="B14" s="170"/>
-      <c r="C14" s="171"/>
+      <c r="C14" s="482"/>
       <c r="D14" s="171"/>
       <c r="E14" s="171"/>
       <c r="F14" s="171"/>
@@ -27921,7 +27628,7 @@
     <row r="15" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" s="169"/>
       <c r="B15" s="170"/>
-      <c r="C15" s="172"/>
+      <c r="C15" s="483"/>
       <c r="D15" s="173"/>
       <c r="E15" s="173"/>
       <c r="F15" s="173"/>
@@ -27948,7 +27655,7 @@
     <row r="16" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="175"/>
       <c r="B16" s="176"/>
-      <c r="C16" s="177"/>
+      <c r="C16" s="484"/>
       <c r="D16" s="177"/>
       <c r="E16" s="177"/>
       <c r="F16" s="177"/>
@@ -27975,7 +27682,7 @@
     <row r="17" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" s="178"/>
       <c r="B17" s="179"/>
-      <c r="C17" s="180"/>
+      <c r="C17" s="485"/>
       <c r="D17" s="181"/>
       <c r="E17" s="181"/>
       <c r="F17" s="181"/>
@@ -28002,7 +27709,7 @@
     <row r="18" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" s="183"/>
       <c r="B18" s="184"/>
-      <c r="C18" s="185"/>
+      <c r="C18" s="486"/>
       <c r="D18" s="185"/>
       <c r="E18" s="185"/>
       <c r="F18" s="185"/>
@@ -28029,7 +27736,7 @@
     <row r="19" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" s="186"/>
       <c r="B19" s="176"/>
-      <c r="C19" s="177"/>
+      <c r="C19" s="484"/>
       <c r="D19" s="177"/>
       <c r="E19" s="177"/>
       <c r="F19" s="177"/>
@@ -28056,7 +27763,7 @@
     <row r="20" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" s="169"/>
       <c r="B20" s="176"/>
-      <c r="C20" s="177"/>
+      <c r="C20" s="484"/>
       <c r="D20" s="177"/>
       <c r="E20" s="177"/>
       <c r="F20" s="177"/>
@@ -28083,7 +27790,7 @@
     <row r="21" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" s="187"/>
       <c r="B21" s="176"/>
-      <c r="C21" s="177"/>
+      <c r="C21" s="484"/>
       <c r="D21" s="177"/>
       <c r="E21" s="177"/>
       <c r="F21" s="177"/>
@@ -28110,7 +27817,7 @@
     <row r="22" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" s="188"/>
       <c r="B22" s="189"/>
-      <c r="C22" s="190"/>
+      <c r="C22" s="487"/>
       <c r="D22" s="190"/>
       <c r="E22" s="190"/>
       <c r="F22" s="190"/>
@@ -28137,7 +27844,7 @@
     <row r="23" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" s="183"/>
       <c r="B23" s="58"/>
-      <c r="C23" s="185"/>
+      <c r="C23" s="486"/>
       <c r="D23" s="185"/>
       <c r="E23" s="185"/>
       <c r="F23" s="185"/>
@@ -28164,7 +27871,7 @@
     <row r="24" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" s="191"/>
       <c r="B24" s="176"/>
-      <c r="C24" s="177"/>
+      <c r="C24" s="484"/>
       <c r="D24" s="177"/>
       <c r="E24" s="177"/>
       <c r="F24" s="177"/>
@@ -28191,7 +27898,7 @@
     <row r="25" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" s="175"/>
       <c r="B25" s="176"/>
-      <c r="C25" s="177"/>
+      <c r="C25" s="484"/>
       <c r="D25" s="177"/>
       <c r="E25" s="177"/>
       <c r="F25" s="177"/>
@@ -28218,7 +27925,7 @@
     <row r="26" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" s="169"/>
       <c r="B26" s="176"/>
-      <c r="C26" s="177"/>
+      <c r="C26" s="484"/>
       <c r="D26" s="177"/>
       <c r="E26" s="177"/>
       <c r="F26" s="177"/>
@@ -28245,7 +27952,7 @@
     <row r="27" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27" s="192"/>
       <c r="B27" s="189"/>
-      <c r="C27" s="190"/>
+      <c r="C27" s="487"/>
       <c r="D27" s="190"/>
       <c r="E27" s="190"/>
       <c r="F27" s="190"/>
@@ -28272,7 +27979,7 @@
     <row r="28" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" s="169"/>
       <c r="B28" s="176"/>
-      <c r="C28" s="177"/>
+      <c r="C28" s="484"/>
       <c r="D28" s="177"/>
       <c r="E28" s="177"/>
       <c r="F28" s="177"/>
@@ -28301,7 +28008,7 @@
         <v>35</v>
       </c>
       <c r="B29" s="170"/>
-      <c r="C29" s="172"/>
+      <c r="C29" s="483"/>
       <c r="D29" s="173"/>
       <c r="E29" s="173"/>
       <c r="F29" s="173"/>
@@ -28328,7 +28035,7 @@
     <row r="30" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" s="187"/>
       <c r="B30" s="176"/>
-      <c r="C30" s="177"/>
+      <c r="C30" s="484"/>
       <c r="D30" s="177"/>
       <c r="E30" s="177"/>
       <c r="F30" s="177"/>
@@ -28355,7 +28062,7 @@
     <row r="31" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" s="193"/>
       <c r="B31" s="176"/>
-      <c r="C31" s="177"/>
+      <c r="C31" s="484"/>
       <c r="D31" s="177"/>
       <c r="E31" s="177"/>
       <c r="F31" s="177"/>
@@ -28382,7 +28089,7 @@
     <row r="32" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32" s="178"/>
       <c r="B32" s="189"/>
-      <c r="C32" s="180"/>
+      <c r="C32" s="485"/>
       <c r="D32" s="181"/>
       <c r="E32" s="181"/>
       <c r="F32" s="181"/>
@@ -28409,7 +28116,7 @@
     <row r="33" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" s="183"/>
       <c r="B33" s="176"/>
-      <c r="C33" s="177"/>
+      <c r="C33" s="484"/>
       <c r="D33" s="177"/>
       <c r="E33" s="177"/>
       <c r="F33" s="177"/>
@@ -28436,7 +28143,7 @@
     <row r="34" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34" s="169"/>
       <c r="B34" s="176"/>
-      <c r="C34" s="177"/>
+      <c r="C34" s="484"/>
       <c r="D34" s="177"/>
       <c r="E34" s="177"/>
       <c r="F34" s="177"/>
@@ -28463,7 +28170,7 @@
     <row r="35" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35" s="187"/>
       <c r="B35" s="176"/>
-      <c r="C35" s="177"/>
+      <c r="C35" s="484"/>
       <c r="D35" s="177"/>
       <c r="E35" s="177"/>
       <c r="F35" s="177"/>
@@ -28490,7 +28197,7 @@
     <row r="36" ht="20.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36" s="186"/>
       <c r="B36" s="176"/>
-      <c r="C36" s="177"/>
+      <c r="C36" s="484"/>
       <c r="D36" s="177"/>
       <c r="E36" s="177"/>
       <c r="F36" s="177"/>
@@ -28517,7 +28224,7 @@
     <row r="37" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37" s="194"/>
       <c r="B37" s="189"/>
-      <c r="C37" s="190"/>
+      <c r="C37" s="487"/>
       <c r="D37" s="190"/>
       <c r="E37" s="190"/>
       <c r="F37" s="190"/>
@@ -28544,7 +28251,7 @@
     <row r="38" ht="20.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38" s="191"/>
       <c r="B38" s="176"/>
-      <c r="C38" s="177"/>
+      <c r="C38" s="484"/>
       <c r="D38" s="177"/>
       <c r="E38" s="177"/>
       <c r="F38" s="177"/>
@@ -28571,7 +28278,7 @@
     <row r="39" ht="20.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39" s="175"/>
       <c r="B39" s="176"/>
-      <c r="C39" s="177"/>
+      <c r="C39" s="484"/>
       <c r="D39" s="177"/>
       <c r="E39" s="177"/>
       <c r="F39" s="177"/>
@@ -28598,7 +28305,7 @@
     <row r="40" ht="20.1" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40" s="169"/>
       <c r="B40" s="176"/>
-      <c r="C40" s="177"/>
+      <c r="C40" s="484"/>
       <c r="D40" s="177"/>
       <c r="E40" s="177"/>
       <c r="F40" s="177"/>
@@ -28625,7 +28332,7 @@
     <row r="41" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A41" s="193"/>
       <c r="B41" s="176"/>
-      <c r="C41" s="177"/>
+      <c r="C41" s="484"/>
       <c r="D41" s="177"/>
       <c r="E41" s="177"/>
       <c r="F41" s="177"/>
@@ -28652,7 +28359,7 @@
     <row r="42" ht="18" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A42" s="191"/>
       <c r="B42" s="58"/>
-      <c r="C42" s="185"/>
+      <c r="C42" s="486"/>
       <c r="D42" s="185"/>
       <c r="E42" s="185"/>
       <c r="F42" s="185"/>
@@ -28922,7 +28629,7 @@
       <c r="Y51" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="41">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="C3:F3"/>
@@ -28962,6 +28669,8 @@
     <mergeCell ref="C42:H42"/>
     <mergeCell ref="A46:B46"/>
     <mergeCell ref="G46:H46"/>
+    <mergeCell ref="C43:H43"/>
+    <mergeCell ref="C44:H44"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.3937007874015748" bottom="0.3937007874015748" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -28970,7 +28679,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -29643,7 +29352,7 @@
       <c r="A4" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B4" s="201" t="s">
+      <c r="B4" s="168" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="201"/>
@@ -29652,7 +29361,7 @@
       <c r="F4" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="G4" s="200"/>
+      <c r="G4" s="489"/>
       <c r="H4" s="8"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
@@ -29703,7 +29412,7 @@
       <c r="A6" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="168" t="s">
         <v>60</v>
       </c>
       <c r="C6" s="8"/>
@@ -29714,7 +29423,7 @@
       <c r="F6" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="G6" s="335" t="s">
+      <c r="G6" s="500" t="s">
         <v>25</v>
       </c>
       <c r="H6" s="3"/>
@@ -30357,12 +30066,12 @@
     <row r="29" ht="21.9" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" s="360"/>
       <c r="B29" s="361"/>
-      <c r="C29" s="362"/>
-      <c r="D29" s="362"/>
-      <c r="E29" s="362"/>
-      <c r="F29" s="362"/>
-      <c r="G29" s="362"/>
-      <c r="H29" s="362"/>
+      <c r="C29" s="501"/>
+      <c r="D29" s="501"/>
+      <c r="E29" s="501"/>
+      <c r="F29" s="501"/>
+      <c r="G29" s="501"/>
+      <c r="H29" s="501"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
@@ -30384,12 +30093,12 @@
     <row r="30" ht="21.9" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" s="360"/>
       <c r="B30" s="361"/>
-      <c r="C30" s="362"/>
-      <c r="D30" s="362"/>
-      <c r="E30" s="362"/>
-      <c r="F30" s="362"/>
-      <c r="G30" s="362"/>
-      <c r="H30" s="362"/>
+      <c r="C30" s="501"/>
+      <c r="D30" s="501"/>
+      <c r="E30" s="501"/>
+      <c r="F30" s="501"/>
+      <c r="G30" s="501"/>
+      <c r="H30" s="501"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
@@ -30411,12 +30120,12 @@
     <row r="31" ht="21.9" customHeight="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" s="360"/>
       <c r="B31" s="361"/>
-      <c r="C31" s="362"/>
-      <c r="D31" s="362"/>
-      <c r="E31" s="362"/>
-      <c r="F31" s="362"/>
-      <c r="G31" s="362"/>
-      <c r="H31" s="362"/>
+      <c r="C31" s="501"/>
+      <c r="D31" s="501"/>
+      <c r="E31" s="501"/>
+      <c r="F31" s="501"/>
+      <c r="G31" s="501"/>
+      <c r="H31" s="501"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
@@ -30719,7 +30428,7 @@
       <c r="F41" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="G41" s="200">
+      <c r="G41" s="489">
         <v>46225</v>
       </c>
       <c r="H41" s="8"/>
@@ -30772,7 +30481,7 @@
       <c r="A43" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="168" t="s">
         <v>84</v>
       </c>
       <c r="C43" s="8"/>
@@ -30783,7 +30492,7 @@
       <c r="F43" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="G43" s="335" t="s">
+      <c r="G43" s="500" t="s">
         <v>25</v>
       </c>
       <c r="H43" s="3"/>
